--- a/data/k-props/2026-08-17.xlsx
+++ b/data/k-props/2026-08-17.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="78">
   <si>
     <t>date</t>
   </si>
@@ -133,6 +133,15 @@
     <t>08/17/2026</t>
   </si>
   <si>
+    <t>Quinn Mathews</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Shane McClanahan</t>
   </si>
   <si>
@@ -145,25 +154,43 @@
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>&lt;6</t>
   </si>
   <si>
     <t>Brandon Young</t>
   </si>
   <si>
+    <t>Cristopher Sanchez</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Janson Junk</t>
+  </si>
+  <si>
+    <t>Andre Pallante</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Carmen Mlodzinski</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
     <t>Framber Valdez</t>
   </si>
   <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Carmen Mlodzinski</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
   </si>
   <si>
     <t>Walker Buehler</t>
@@ -175,15 +202,24 @@
     <t>Nolan McLean</t>
   </si>
   <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Mason Barnett</t>
+  </si>
+  <si>
+    <t>Martin Perez</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
     <t>Bailey Ober</t>
   </si>
   <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Martin Perez</t>
-  </si>
-  <si>
     <t>Luis Castillo</t>
   </si>
   <si>
@@ -202,37 +238,10 @@
     <t>Blake Snell</t>
   </si>
   <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Janson Junk</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
     <t>Cristopher Sánchez</t>
   </si>
   <si>
     <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Mason Barnett</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
   </si>
   <si>
     <t>Martín Pérez</t>
@@ -616,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM20"/>
+  <dimension ref="A1:AM23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -749,97 +758,40 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2">
-        <v>117</v>
+        <v>-111</v>
       </c>
       <c r="E2">
-        <v>-150</v>
+        <v>-102</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
-      <c r="G2">
-        <v>822939</v>
+      <c r="G2" t="s">
+        <v>42</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
       <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0.2225</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="O2">
-        <v>97</v>
-      </c>
-      <c r="P2">
-        <v>4.13</v>
-      </c>
-      <c r="Q2">
-        <v>0.1856</v>
-      </c>
-      <c r="R2">
-        <v>0.327</v>
+        <v>6</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2">
-        <v>0.2817</v>
-      </c>
-      <c r="U2">
-        <v>0.2457</v>
-      </c>
-      <c r="V2">
-        <v>8</v>
-      </c>
-      <c r="W2">
-        <v>0.2564</v>
-      </c>
-      <c r="X2">
-        <v>0.2197</v>
-      </c>
-      <c r="Y2">
-        <v>1.0287</v>
+        <v>42</v>
+      </c>
+      <c r="V2" t="s">
+        <v>42</v>
       </c>
       <c r="AA2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD2">
-        <v>5.68</v>
+        <v>42</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF2">
-        <v>0.2104</v>
-      </c>
-      <c r="AG2">
-        <v>1.282</v>
-      </c>
-      <c r="AH2">
-        <v>0.16</v>
-      </c>
-      <c r="AM2">
-        <v>5.84</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -847,28 +799,28 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C3">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-124</v>
+        <v>-115</v>
       </c>
       <c r="E3">
-        <v>-103</v>
+        <v>100</v>
       </c>
       <c r="F3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G3">
         <v>822939</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I3">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -877,70 +829,70 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M3">
-        <v>0.191</v>
+        <v>0.2225</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>124</v>
+        <v>97</v>
       </c>
       <c r="P3">
-        <v>4.28</v>
+        <v>4.13</v>
       </c>
       <c r="Q3">
-        <v>0.2097</v>
+        <v>0.1856</v>
       </c>
       <c r="R3">
-        <v>0.383</v>
+        <v>0.327</v>
       </c>
       <c r="S3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T3">
-        <v>0.1804</v>
+        <v>0.2848</v>
       </c>
       <c r="U3">
-        <v>0.1772</v>
+        <v>0.2531</v>
       </c>
       <c r="V3">
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.1892</v>
+        <v>0.2564</v>
       </c>
       <c r="X3">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y3">
-        <v>0.9056</v>
+        <v>1.0211</v>
       </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD3">
-        <v>3.59</v>
+        <v>5.59</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF3">
-        <v>0.1981</v>
+        <v>0.2104</v>
       </c>
       <c r="AG3">
-        <v>0.8208</v>
+        <v>1.2717</v>
       </c>
       <c r="AH3">
         <v>0.16</v>
       </c>
       <c r="AM3">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -948,28 +900,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>109</v>
+        <v>-127</v>
       </c>
       <c r="E4">
-        <v>-140</v>
+        <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>823343</v>
+        <v>822939</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -978,70 +930,70 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M4">
-        <v>0.1806</v>
+        <v>0.191</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="P4">
-        <v>4.41</v>
+        <v>4.28</v>
       </c>
       <c r="Q4">
-        <v>0.161</v>
+        <v>0.2097</v>
       </c>
       <c r="R4">
-        <v>0.371</v>
+        <v>0.383</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T4">
-        <v>0.2135</v>
+        <v>0.1804</v>
       </c>
       <c r="U4">
-        <v>0.2374</v>
+        <v>0.1772</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2552</v>
+        <v>0.1892</v>
       </c>
       <c r="X4">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y4">
-        <v>1.0456</v>
+        <v>0.9068</v>
       </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD4">
-        <v>4.31</v>
+        <v>3.52</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF4">
-        <v>0.1733</v>
+        <v>0.1981</v>
       </c>
       <c r="AG4">
-        <v>0.9716</v>
+        <v>0.8054</v>
       </c>
       <c r="AH4">
         <v>0.16</v>
       </c>
       <c r="AM4">
-        <v>4.47</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1052,97 +1004,40 @@
         <v>49</v>
       </c>
       <c r="C5">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="D5">
-        <v>-134</v>
+        <v>-140</v>
       </c>
       <c r="E5">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5">
-        <v>823343</v>
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>42</v>
       </c>
       <c r="H5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5">
-        <v>4.5</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>0.1801</v>
-      </c>
-      <c r="N5">
-        <v>5</v>
-      </c>
-      <c r="O5">
-        <v>95</v>
-      </c>
-      <c r="P5">
-        <v>4.34</v>
-      </c>
-      <c r="Q5">
-        <v>0.0632</v>
-      </c>
-      <c r="R5">
-        <v>0.322</v>
+        <v>6</v>
       </c>
       <c r="S5" t="s">
-        <v>43</v>
-      </c>
-      <c r="T5">
-        <v>0.187</v>
-      </c>
-      <c r="U5">
-        <v>0.1952</v>
-      </c>
-      <c r="V5">
-        <v>9</v>
-      </c>
-      <c r="W5">
-        <v>0.2248</v>
-      </c>
-      <c r="X5">
-        <v>0.2197</v>
-      </c>
-      <c r="Y5">
-        <v>0.9825</v>
+        <v>42</v>
+      </c>
+      <c r="V5" t="s">
+        <v>42</v>
       </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD5">
-        <v>2.49</v>
+        <v>42</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF5">
-        <v>0.1531</v>
-      </c>
-      <c r="AG5">
-        <v>0.8511</v>
-      </c>
-      <c r="AH5">
-        <v>0.16</v>
-      </c>
-      <c r="AM5">
-        <v>2.65</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1156,22 +1051,22 @@
         <v>3.5</v>
       </c>
       <c r="D6">
-        <v>-142</v>
+        <v>132</v>
       </c>
       <c r="E6">
-        <v>122</v>
+        <v>-150</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G6">
-        <v>823589</v>
+        <v>823427</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I6">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
@@ -1180,70 +1075,70 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>0.2012</v>
+        <v>0.1716</v>
       </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="P6">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="Q6">
-        <v>0.1743</v>
+        <v>0.1649</v>
       </c>
       <c r="R6">
-        <v>0.353</v>
+        <v>0.327</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T6">
-        <v>0.2494</v>
+        <v>0.1805</v>
       </c>
       <c r="U6">
-        <v>0.2434</v>
+        <v>0.1815</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>0.225</v>
+        <v>0.2246</v>
       </c>
       <c r="X6">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y6">
-        <v>0.9809</v>
+        <v>0.9677</v>
       </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD6">
-        <v>4.42</v>
+        <v>2.9</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF6">
-        <v>0.1917</v>
+        <v>0.1694</v>
       </c>
       <c r="AG6">
-        <v>1.1351</v>
+        <v>0.8059</v>
       </c>
       <c r="AH6">
         <v>0.16</v>
       </c>
       <c r="AM6">
-        <v>4.58</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1251,25 +1146,25 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D7">
-        <v>-153</v>
+        <v>-108</v>
       </c>
       <c r="E7">
-        <v>128</v>
+        <v>-118</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G7">
-        <v>823589</v>
+        <v>824478</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I7">
         <v>5.7</v>
@@ -1281,70 +1176,70 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>0.2799</v>
+        <v>0.1707</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="P7">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="Q7">
-        <v>0.2833</v>
+        <v>0.1724</v>
       </c>
       <c r="R7">
-        <v>0.375</v>
+        <v>0.367</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T7">
-        <v>0.1541</v>
+        <v>0.2529</v>
       </c>
       <c r="U7">
-        <v>0.1718</v>
+        <v>0.2629</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2171</v>
+        <v>0.2542</v>
       </c>
       <c r="X7">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y7">
-        <v>0.9952</v>
+        <v>1.0317</v>
       </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD7">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF7">
-        <v>0.2812</v>
+        <v>0.1713</v>
       </c>
       <c r="AG7">
-        <v>0.7015</v>
+        <v>1.1294</v>
       </c>
       <c r="AH7">
         <v>0.16</v>
       </c>
       <c r="AM7">
-        <v>4.81</v>
+        <v>4.84</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1352,28 +1247,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D8">
-        <v>-124</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>-103</v>
+        <v>-156</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G8">
-        <v>823668</v>
+        <v>824478</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I8">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1382,70 +1277,70 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>0.1614</v>
+        <v>0.182</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="P8">
-        <v>4.19</v>
+        <v>4.48</v>
       </c>
       <c r="Q8">
-        <v>0.1391</v>
+        <v>0.1698</v>
       </c>
       <c r="R8">
-        <v>0.365</v>
+        <v>0.346</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T8">
-        <v>0.2315</v>
+        <v>0.1968</v>
       </c>
       <c r="U8">
-        <v>0.2236</v>
+        <v>0.1856</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2177</v>
+        <v>0.2124</v>
       </c>
       <c r="X8">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y8">
-        <v>0.9704</v>
+        <v>0.9658</v>
       </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD8">
-        <v>3.61</v>
+        <v>3.28</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF8">
-        <v>0.1533</v>
+        <v>0.1778</v>
       </c>
       <c r="AG8">
-        <v>1.0538</v>
+        <v>0.8788</v>
       </c>
       <c r="AH8">
         <v>0.16</v>
       </c>
       <c r="AM8">
-        <v>3.77</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1453,43 +1348,100 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="D9">
-        <v>-113</v>
+        <v>-150</v>
       </c>
       <c r="E9">
-        <v>-112</v>
+        <v>130</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
       </c>
-      <c r="G9" t="s">
-        <v>44</v>
+      <c r="G9">
+        <v>823343</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="I9">
+        <v>4.5</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="M9">
+        <v>0.1801</v>
+      </c>
+      <c r="N9">
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <v>95</v>
+      </c>
+      <c r="P9">
+        <v>4.34</v>
+      </c>
+      <c r="Q9">
+        <v>0.0632</v>
+      </c>
+      <c r="R9">
+        <v>0.322</v>
       </c>
       <c r="S9" t="s">
-        <v>44</v>
-      </c>
-      <c r="V9" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="T9">
+        <v>0.187</v>
+      </c>
+      <c r="U9">
+        <v>0.1952</v>
+      </c>
+      <c r="V9">
+        <v>9</v>
+      </c>
+      <c r="W9">
+        <v>0.2248</v>
+      </c>
+      <c r="X9">
+        <v>0.2239</v>
+      </c>
+      <c r="Y9">
+        <v>0.9826</v>
       </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="AD9">
+        <v>2.45</v>
       </c>
       <c r="AE9" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="AF9">
+        <v>0.1531</v>
+      </c>
+      <c r="AG9">
+        <v>0.8351</v>
+      </c>
+      <c r="AH9">
+        <v>0.16</v>
+      </c>
+      <c r="AM9">
+        <v>2.61</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1500,25 +1452,25 @@
         <v>57</v>
       </c>
       <c r="C10">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D10">
-        <v>-104</v>
+        <v>118</v>
       </c>
       <c r="E10">
-        <v>-113</v>
+        <v>-143</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G10">
-        <v>824641</v>
+        <v>823343</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I10">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1527,70 +1479,70 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2087</v>
+        <v>0.1806</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P10">
-        <v>4.37</v>
+        <v>4.41</v>
       </c>
       <c r="Q10">
-        <v>0.2017</v>
+        <v>0.161</v>
       </c>
       <c r="R10">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T10">
-        <v>0.2302</v>
+        <v>0.2135</v>
       </c>
       <c r="U10">
-        <v>0.2283</v>
+        <v>0.2374</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>0.2179</v>
+        <v>0.2552</v>
       </c>
       <c r="X10">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y10">
-        <v>0.9623</v>
+        <v>1.0441</v>
       </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD10">
-        <v>4.75</v>
+        <v>4.22</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF10">
-        <v>0.2061</v>
+        <v>0.1733</v>
       </c>
       <c r="AG10">
-        <v>1.0475</v>
+        <v>0.9533</v>
       </c>
       <c r="AH10">
         <v>0.16</v>
       </c>
       <c r="AM10">
-        <v>4.91</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1598,28 +1550,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11">
+        <v>3.5</v>
+      </c>
+      <c r="D11">
+        <v>-142</v>
+      </c>
+      <c r="E11">
+        <v>112</v>
+      </c>
+      <c r="F11" t="s">
         <v>59</v>
       </c>
-      <c r="C11">
-        <v>5.5</v>
-      </c>
-      <c r="D11">
-        <v>-128</v>
-      </c>
-      <c r="E11">
-        <v>103</v>
-      </c>
-      <c r="F11" t="s">
-        <v>58</v>
-      </c>
       <c r="G11">
-        <v>824641</v>
+        <v>824725</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I11">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
@@ -1628,70 +1580,70 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>0.2347</v>
+        <v>0.1748</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P11">
-        <v>4.03</v>
+        <v>4.25</v>
       </c>
       <c r="Q11">
-        <v>0.2155</v>
+        <v>0.1913</v>
       </c>
       <c r="R11">
-        <v>0.367</v>
+        <v>0.365</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T11">
-        <v>0.2179</v>
+        <v>0.2109</v>
       </c>
       <c r="U11">
-        <v>0.2366</v>
+        <v>0.1979</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2442</v>
+        <v>0.2169</v>
       </c>
       <c r="X11">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y11">
-        <v>1.0244</v>
+        <v>0.9913</v>
       </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD11">
-        <v>5.34</v>
+        <v>3.45</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF11">
-        <v>0.2276</v>
+        <v>0.1808</v>
       </c>
       <c r="AG11">
-        <v>0.9916</v>
+        <v>0.9419</v>
       </c>
       <c r="AH11">
         <v>0.16</v>
       </c>
       <c r="AM11">
-        <v>5.5</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1702,10 +1654,10 @@
         <v>60</v>
       </c>
       <c r="C12">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="D12">
-        <v>-156</v>
+        <v>-148</v>
       </c>
       <c r="E12">
         <v>122</v>
@@ -1714,13 +1666,13 @@
         <v>61</v>
       </c>
       <c r="G12">
-        <v>824320</v>
+        <v>823589</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I12">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="b">
         <v>0</v>
@@ -1729,70 +1681,70 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>0.1392</v>
+        <v>0.2012</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="P12">
-        <v>4.17</v>
+        <v>4.35</v>
       </c>
       <c r="Q12">
-        <v>0.1552</v>
+        <v>0.1743</v>
       </c>
       <c r="R12">
-        <v>0.367</v>
+        <v>0.353</v>
       </c>
       <c r="S12" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T12">
-        <v>0.2857</v>
+        <v>0.2494</v>
       </c>
       <c r="U12">
-        <v>0.2224</v>
+        <v>0.2434</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.2074</v>
+        <v>0.225</v>
       </c>
       <c r="X12">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y12">
-        <v>1.0069</v>
+        <v>0.9812</v>
       </c>
       <c r="AA12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD12">
-        <v>4.29</v>
+        <v>4.34</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF12">
-        <v>0.1451</v>
+        <v>0.1917</v>
       </c>
       <c r="AG12">
-        <v>1.3002</v>
+        <v>1.1137</v>
       </c>
       <c r="AH12">
         <v>0.16</v>
       </c>
       <c r="AM12">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1803,40 +1755,97 @@
         <v>62</v>
       </c>
       <c r="C13">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D13">
-        <v>-130</v>
+        <v>-139</v>
       </c>
       <c r="E13">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="F13" t="s">
         <v>61</v>
       </c>
-      <c r="G13" t="s">
-        <v>44</v>
+      <c r="G13">
+        <v>823589</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="I13">
+        <v>5.7</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="M13">
+        <v>0.2799</v>
+      </c>
+      <c r="N13">
+        <v>5</v>
+      </c>
+      <c r="O13">
+        <v>120</v>
+      </c>
+      <c r="P13">
+        <v>4.16</v>
+      </c>
+      <c r="Q13">
+        <v>0.2833</v>
+      </c>
+      <c r="R13">
+        <v>0.375</v>
       </c>
       <c r="S13" t="s">
-        <v>44</v>
-      </c>
-      <c r="V13" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="T13">
+        <v>0.1541</v>
+      </c>
+      <c r="U13">
+        <v>0.1718</v>
+      </c>
+      <c r="V13">
+        <v>9</v>
+      </c>
+      <c r="W13">
+        <v>0.2171</v>
+      </c>
+      <c r="X13">
+        <v>0.2239</v>
+      </c>
+      <c r="Y13">
+        <v>0.9938</v>
       </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="AD13">
+        <v>4.55</v>
       </c>
       <c r="AE13" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="AF13">
+        <v>0.2812</v>
+      </c>
+      <c r="AG13">
+        <v>0.6883</v>
+      </c>
+      <c r="AH13">
+        <v>0.16</v>
+      </c>
+      <c r="AM13">
+        <v>4.71</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1846,17 +1855,26 @@
       <c r="B14" t="s">
         <v>63</v>
       </c>
+      <c r="C14">
+        <v>4.5</v>
+      </c>
+      <c r="D14">
+        <v>103</v>
+      </c>
+      <c r="E14">
+        <v>-115</v>
+      </c>
       <c r="F14" t="s">
         <v>64</v>
       </c>
       <c r="G14">
-        <v>824478</v>
+        <v>824077</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I14">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1865,70 +1883,70 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M14">
-        <v>0.182</v>
+        <v>0.1912</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="P14">
-        <v>4.48</v>
+        <v>4.06</v>
       </c>
       <c r="Q14">
-        <v>0.1698</v>
+        <v>0.168</v>
       </c>
       <c r="R14">
-        <v>0.346</v>
+        <v>0.385</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T14">
-        <v>0.1968</v>
+        <v>0.2534</v>
       </c>
       <c r="U14">
-        <v>0.1856</v>
+        <v>0.2192</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2124</v>
+        <v>0.2153</v>
       </c>
       <c r="X14">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y14">
-        <v>0.9651</v>
+        <v>1.0228</v>
       </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD14">
-        <v>3.34</v>
+        <v>5.38</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF14">
-        <v>0.1778</v>
+        <v>0.1823</v>
       </c>
       <c r="AG14">
-        <v>0.8957</v>
+        <v>1.1315</v>
       </c>
       <c r="AH14">
         <v>0.16</v>
       </c>
       <c r="AM14">
-        <v>3.5</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1938,17 +1956,26 @@
       <c r="B15" t="s">
         <v>65</v>
       </c>
+      <c r="C15">
+        <v>3.5</v>
+      </c>
+      <c r="D15">
+        <v>114</v>
+      </c>
+      <c r="E15">
+        <v>-140</v>
+      </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G15">
-        <v>823427</v>
+        <v>824077</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I15">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1957,70 +1984,70 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>0.1716</v>
+        <v>0.2156</v>
       </c>
       <c r="N15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>97</v>
+        <v>62</v>
       </c>
       <c r="P15">
-        <v>4.25</v>
+        <v>4.39</v>
       </c>
       <c r="Q15">
-        <v>0.1649</v>
+        <v>0.2097</v>
       </c>
       <c r="R15">
-        <v>0.327</v>
+        <v>0.237</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T15">
-        <v>0.1805</v>
+        <v>0.2083</v>
       </c>
       <c r="U15">
-        <v>0.1815</v>
+        <v>0.2106</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>0.2246</v>
+        <v>0.2103</v>
       </c>
       <c r="X15">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y15">
-        <v>0.9683</v>
+        <v>0.9716</v>
       </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD15">
-        <v>2.96</v>
+        <v>3.78</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF15">
-        <v>0.1694</v>
+        <v>0.2142</v>
       </c>
       <c r="AG15">
-        <v>0.8213</v>
+        <v>0.93</v>
       </c>
       <c r="AH15">
         <v>0.16</v>
       </c>
       <c r="AM15">
-        <v>3.12</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2028,91 +2055,43 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16">
+        <v>3.5</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>-108</v>
+      </c>
+      <c r="F16" t="s">
         <v>67</v>
       </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>823427</v>
+      <c r="G16" t="s">
+        <v>42</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
-      <c r="I16">
-        <v>6.2</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
       <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0.2802</v>
-      </c>
-      <c r="N16">
-        <v>5</v>
-      </c>
-      <c r="O16">
-        <v>121</v>
-      </c>
-      <c r="P16">
-        <v>4.15</v>
-      </c>
-      <c r="Q16">
-        <v>0.3058</v>
-      </c>
-      <c r="R16">
-        <v>0.377</v>
+        <v>6</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
-      </c>
-      <c r="T16">
-        <v>0.2386</v>
-      </c>
-      <c r="U16">
-        <v>0.2292</v>
-      </c>
-      <c r="V16">
-        <v>9</v>
-      </c>
-      <c r="W16">
-        <v>0.2314</v>
-      </c>
-      <c r="X16">
-        <v>0.2197</v>
-      </c>
-      <c r="Y16">
-        <v>1.0339</v>
+        <v>42</v>
+      </c>
+      <c r="V16" t="s">
+        <v>42</v>
       </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD16">
-        <v>8.41</v>
+        <v>42</v>
       </c>
       <c r="AE16" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF16">
-        <v>0.2898</v>
-      </c>
-      <c r="AG16">
-        <v>1.086</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>8.41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2120,19 +2099,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="C17">
+        <v>3.5</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>-119</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G17">
-        <v>824725</v>
+        <v>823668</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I17">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2141,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>0.1748</v>
+        <v>0.1614</v>
       </c>
       <c r="N17">
         <v>5</v>
@@ -2153,58 +2141,58 @@
         <v>115</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="Q17">
-        <v>0.1913</v>
+        <v>0.1391</v>
       </c>
       <c r="R17">
         <v>0.365</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T17">
-        <v>0.2109</v>
+        <v>0.2315</v>
       </c>
       <c r="U17">
-        <v>0.1979</v>
+        <v>0.2236</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2169</v>
+        <v>0.2177</v>
       </c>
       <c r="X17">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y17">
-        <v>0.9908</v>
+        <v>0.9695</v>
       </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD17">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF17">
-        <v>0.1808</v>
+        <v>0.1533</v>
       </c>
       <c r="AG17">
-        <v>0.96</v>
+        <v>1.0339</v>
       </c>
       <c r="AH17">
         <v>0.16</v>
       </c>
       <c r="AM17">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2212,19 +2200,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>69</v>
+      </c>
+      <c r="C18">
+        <v>4.5</v>
+      </c>
+      <c r="D18">
+        <v>-115</v>
+      </c>
+      <c r="E18">
+        <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G18">
-        <v>824077</v>
+        <v>824641</v>
       </c>
       <c r="H18" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I18">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2233,70 +2230,70 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2156</v>
+        <v>0.2087</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="P18">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="Q18">
-        <v>0.2097</v>
+        <v>0.2017</v>
       </c>
       <c r="R18">
-        <v>0.237</v>
+        <v>0.373</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T18">
-        <v>0.2083</v>
+        <v>0.2302</v>
       </c>
       <c r="U18">
-        <v>0.2106</v>
+        <v>0.2283</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2103</v>
+        <v>0.2179</v>
       </c>
       <c r="X18">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y18">
-        <v>0.9718</v>
+        <v>0.9619</v>
       </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD18">
-        <v>3.85</v>
+        <v>4.66</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF18">
-        <v>0.2142</v>
+        <v>0.2061</v>
       </c>
       <c r="AG18">
-        <v>0.9478</v>
+        <v>1.0278</v>
       </c>
       <c r="AH18">
         <v>0.16</v>
       </c>
       <c r="AM18">
-        <v>4.01</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2304,19 +2301,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="C19">
+        <v>5.5</v>
+      </c>
+      <c r="D19">
+        <v>-124</v>
+      </c>
+      <c r="E19">
+        <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G19">
-        <v>824077</v>
+        <v>824641</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I19">
-        <v>6.3</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2325,70 +2331,70 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>0.1912</v>
+        <v>0.2347</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="P19">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="Q19">
-        <v>0.168</v>
+        <v>0.2155</v>
       </c>
       <c r="R19">
-        <v>0.385</v>
+        <v>0.367</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T19">
-        <v>0.2534</v>
+        <v>0.2179</v>
       </c>
       <c r="U19">
-        <v>0.2192</v>
+        <v>0.2366</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2153</v>
+        <v>0.2442</v>
       </c>
       <c r="X19">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y19">
-        <v>1.0233</v>
+        <v>1.0245</v>
       </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD19">
-        <v>5.48</v>
+        <v>5.24</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF19">
-        <v>0.1823</v>
+        <v>0.2276</v>
       </c>
       <c r="AG19">
-        <v>1.1532</v>
+        <v>0.9729</v>
       </c>
       <c r="AH19">
         <v>0.16</v>
       </c>
       <c r="AM19">
-        <v>5.64</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2396,19 +2402,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="C20">
+        <v>2.5</v>
+      </c>
+      <c r="D20">
+        <v>-152</v>
+      </c>
+      <c r="E20">
+        <v>122</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="G20">
-        <v>823668</v>
+        <v>824320</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I20">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2417,70 +2432,298 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M20">
-        <v>0.186</v>
+        <v>0.1392</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="P20">
-        <v>4.04</v>
+        <v>4.17</v>
       </c>
       <c r="Q20">
-        <v>0.1856</v>
+        <v>0.1552</v>
       </c>
       <c r="R20">
-        <v>0.327</v>
+        <v>0.367</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="T20">
-        <v>0.2081</v>
+        <v>0.2857</v>
       </c>
       <c r="U20">
-        <v>0.2056</v>
+        <v>0.2224</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2255</v>
+        <v>0.2074</v>
       </c>
       <c r="X20">
-        <v>0.2197</v>
+        <v>0.2239</v>
       </c>
       <c r="Y20">
-        <v>0.984</v>
+        <v>1.0072</v>
       </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AD20">
-        <v>3.58</v>
+        <v>4.21</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="AF20">
-        <v>0.1859</v>
+        <v>0.1451</v>
       </c>
       <c r="AG20">
-        <v>0.9469</v>
+        <v>1.2758</v>
       </c>
       <c r="AH20">
         <v>0.16</v>
       </c>
       <c r="AM20">
-        <v>3.74</v>
+        <v>4.37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21">
+        <v>6.5</v>
+      </c>
+      <c r="D21">
+        <v>-150</v>
+      </c>
+      <c r="E21">
+        <v>120</v>
+      </c>
+      <c r="F21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" t="s">
+        <v>42</v>
+      </c>
+      <c r="L21">
+        <v>6</v>
+      </c>
+      <c r="S21" t="s">
+        <v>42</v>
+      </c>
+      <c r="V21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F22" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22">
+        <v>823427</v>
+      </c>
+      <c r="H22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22">
+        <v>6.2</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0.2802</v>
+      </c>
+      <c r="N22">
+        <v>5</v>
+      </c>
+      <c r="O22">
+        <v>121</v>
+      </c>
+      <c r="P22">
+        <v>4.15</v>
+      </c>
+      <c r="Q22">
+        <v>0.3058</v>
+      </c>
+      <c r="R22">
+        <v>0.377</v>
+      </c>
+      <c r="S22" t="s">
+        <v>46</v>
+      </c>
+      <c r="T22">
+        <v>0.2386</v>
+      </c>
+      <c r="U22">
+        <v>0.2292</v>
+      </c>
+      <c r="V22">
+        <v>9</v>
+      </c>
+      <c r="W22">
+        <v>0.2314</v>
+      </c>
+      <c r="X22">
+        <v>0.2239</v>
+      </c>
+      <c r="Y22">
+        <v>1.0337</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD22">
+        <v>8.25</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF22">
+        <v>0.2898</v>
+      </c>
+      <c r="AG22">
+        <v>1.0656</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23">
+        <v>823668</v>
+      </c>
+      <c r="H23" t="s">
+        <v>45</v>
+      </c>
+      <c r="I23">
+        <v>5.1</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0.186</v>
+      </c>
+      <c r="N23">
+        <v>5</v>
+      </c>
+      <c r="O23">
+        <v>97</v>
+      </c>
+      <c r="P23">
+        <v>4.04</v>
+      </c>
+      <c r="Q23">
+        <v>0.1856</v>
+      </c>
+      <c r="R23">
+        <v>0.327</v>
+      </c>
+      <c r="S23" t="s">
+        <v>46</v>
+      </c>
+      <c r="T23">
+        <v>0.2081</v>
+      </c>
+      <c r="U23">
+        <v>0.2056</v>
+      </c>
+      <c r="V23">
+        <v>9</v>
+      </c>
+      <c r="W23">
+        <v>0.2255</v>
+      </c>
+      <c r="X23">
+        <v>0.2239</v>
+      </c>
+      <c r="Y23">
+        <v>0.9816</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD23">
+        <v>3.5</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF23">
+        <v>0.1859</v>
+      </c>
+      <c r="AG23">
+        <v>0.9291</v>
+      </c>
+      <c r="AH23">
+        <v>0.16</v>
+      </c>
+      <c r="AM23">
+        <v>3.66</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-17.xlsx
+++ b/data/k-props/2026-08-17.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="80">
   <si>
     <t>date</t>
   </si>
@@ -242,6 +242,12 @@
   </si>
   <si>
     <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Alec Gamboa</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
   </si>
   <si>
     <t>Martín Pérez</t>
@@ -625,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AM24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -761,10 +767,10 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-111</v>
+        <v>-118</v>
       </c>
       <c r="E2">
-        <v>-102</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
@@ -906,10 +912,10 @@
         <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-127</v>
+        <v>-132</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
@@ -1007,10 +1013,10 @@
         <v>6.5</v>
       </c>
       <c r="D5">
-        <v>-140</v>
+        <v>-128</v>
       </c>
       <c r="E5">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F5" t="s">
         <v>50</v>
@@ -1051,10 +1057,10 @@
         <v>3.5</v>
       </c>
       <c r="D6">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E6">
-        <v>-150</v>
+        <v>-155</v>
       </c>
       <c r="F6" t="s">
         <v>50</v>
@@ -1155,7 +1161,7 @@
         <v>-108</v>
       </c>
       <c r="E7">
-        <v>-118</v>
+        <v>-115</v>
       </c>
       <c r="F7" t="s">
         <v>41</v>
@@ -1354,10 +1360,10 @@
         <v>2.5</v>
       </c>
       <c r="D9">
-        <v>-150</v>
+        <v>-162</v>
       </c>
       <c r="E9">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F9" t="s">
         <v>55</v>
@@ -1455,7 +1461,7 @@
         <v>5.5</v>
       </c>
       <c r="D10">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E10">
         <v>-143</v>
@@ -1559,7 +1565,7 @@
         <v>-142</v>
       </c>
       <c r="E11">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
         <v>59</v>
@@ -1660,7 +1666,7 @@
         <v>-148</v>
       </c>
       <c r="E12">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F12" t="s">
         <v>61</v>
@@ -1758,10 +1764,10 @@
         <v>5.5</v>
       </c>
       <c r="D13">
-        <v>-139</v>
+        <v>-147</v>
       </c>
       <c r="E13">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F13" t="s">
         <v>61</v>
@@ -1862,7 +1868,7 @@
         <v>103</v>
       </c>
       <c r="E14">
-        <v>-115</v>
+        <v>-125</v>
       </c>
       <c r="F14" t="s">
         <v>64</v>
@@ -1963,7 +1969,7 @@
         <v>114</v>
       </c>
       <c r="E15">
-        <v>-140</v>
+        <v>-139</v>
       </c>
       <c r="F15" t="s">
         <v>64</v>
@@ -2061,10 +2067,10 @@
         <v>3.5</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="E16">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="F16" t="s">
         <v>67</v>
@@ -2307,7 +2313,7 @@
         <v>5.5</v>
       </c>
       <c r="D19">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="E19">
         <v>110</v>
@@ -2411,7 +2417,7 @@
         <v>-152</v>
       </c>
       <c r="E20">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="F20" t="s">
         <v>73</v>
@@ -2509,10 +2515,10 @@
         <v>6.5</v>
       </c>
       <c r="D21">
-        <v>-150</v>
+        <v>-148</v>
       </c>
       <c r="E21">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
         <v>73</v>
@@ -2642,19 +2648,19 @@
         <v>77</v>
       </c>
       <c r="F23" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G23">
-        <v>823668</v>
+        <v>824725</v>
       </c>
       <c r="H23" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="I23">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="b">
         <v>0</v>
@@ -2663,43 +2669,31 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0.186</v>
-      </c>
-      <c r="N23">
-        <v>5</v>
-      </c>
-      <c r="O23">
-        <v>97</v>
+        <v>0.1765</v>
       </c>
       <c r="P23">
-        <v>4.04</v>
-      </c>
-      <c r="Q23">
-        <v>0.1856</v>
-      </c>
-      <c r="R23">
-        <v>0.327</v>
+        <v>4</v>
       </c>
       <c r="S23" t="s">
         <v>46</v>
       </c>
       <c r="T23">
-        <v>0.2081</v>
+        <v>0.1775</v>
       </c>
       <c r="U23">
-        <v>0.2056</v>
+        <v>0.1778</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2255</v>
+        <v>0.1745</v>
       </c>
       <c r="X23">
         <v>0.2239</v>
       </c>
       <c r="Y23">
-        <v>0.9816</v>
+        <v>0.912</v>
       </c>
       <c r="AA23" t="s">
         <v>42</v>
@@ -2708,21 +2702,113 @@
         <v>42</v>
       </c>
       <c r="AD23">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="AE23" t="s">
         <v>47</v>
       </c>
       <c r="AF23">
-        <v>0.1859</v>
+        <v>0.1765</v>
       </c>
       <c r="AG23">
-        <v>0.9291</v>
+        <v>0.7928</v>
       </c>
       <c r="AH23">
         <v>0.16</v>
       </c>
       <c r="AM23">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
+        <v>79</v>
+      </c>
+      <c r="F24" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24">
+        <v>823668</v>
+      </c>
+      <c r="H24" t="s">
+        <v>45</v>
+      </c>
+      <c r="I24">
+        <v>5.1</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0.186</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>97</v>
+      </c>
+      <c r="P24">
+        <v>4.04</v>
+      </c>
+      <c r="Q24">
+        <v>0.1856</v>
+      </c>
+      <c r="R24">
+        <v>0.327</v>
+      </c>
+      <c r="S24" t="s">
+        <v>46</v>
+      </c>
+      <c r="T24">
+        <v>0.2081</v>
+      </c>
+      <c r="U24">
+        <v>0.2056</v>
+      </c>
+      <c r="V24">
+        <v>9</v>
+      </c>
+      <c r="W24">
+        <v>0.2255</v>
+      </c>
+      <c r="X24">
+        <v>0.2239</v>
+      </c>
+      <c r="Y24">
+        <v>0.9816</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD24">
+        <v>3.5</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF24">
+        <v>0.1859</v>
+      </c>
+      <c r="AG24">
+        <v>0.9291</v>
+      </c>
+      <c r="AH24">
+        <v>0.16</v>
+      </c>
+      <c r="AM24">
         <v>3.66</v>
       </c>
     </row>

--- a/data/k-props/2026-08-17.xlsx
+++ b/data/k-props/2026-08-17.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="81">
   <si>
     <t>date</t>
   </si>
@@ -133,124 +133,127 @@
     <t>08/17/2026</t>
   </si>
   <si>
+    <t>Andre Pallante</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>Janson Junk</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Carmen Mlodzinski</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Alec Gamboa</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
+  </si>
+  <si>
+    <t>Walker Buehler</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>Nolan McLean</t>
+  </si>
+  <si>
+    <t>Mason Barnett</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Michael Wacha</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Bailey Ober</t>
+  </si>
+  <si>
+    <t>Luis Castillo</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Shota Imanaga</t>
+  </si>
+  <si>
+    <t>Tomoyuki Sugano</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
     <t>Quinn Mathews</t>
   </si>
   <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Shane McClanahan</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
     <t>Cristopher Sanchez</t>
   </si>
   <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Janson Junk</t>
-  </si>
-  <si>
-    <t>Andre Pallante</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Carmen Mlodzinski</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Walker Buehler</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ New York Mets</t>
-  </si>
-  <si>
-    <t>Nolan McLean</t>
-  </si>
-  <si>
-    <t>Michael Wacha</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Mason Barnett</t>
-  </si>
-  <si>
     <t>Martin Perez</t>
   </si>
   <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Bailey Ober</t>
-  </si>
-  <si>
-    <t>Luis Castillo</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Shota Imanaga</t>
-  </si>
-  <si>
-    <t>Tomoyuki Sugano</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
     <t>Blake Snell</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Alec Gamboa</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
-  </si>
-  <si>
-    <t>Martín Pérez</t>
   </si>
 </sst>
 </file>
@@ -767,37 +770,94 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>-118</v>
+        <v>-108</v>
       </c>
       <c r="E2">
-        <v>119</v>
+        <v>-115</v>
       </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
-      <c r="G2" t="s">
-        <v>42</v>
+      <c r="G2">
+        <v>824478</v>
       </c>
       <c r="H2" t="s">
         <v>42</v>
       </c>
+      <c r="I2">
+        <v>5.7</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>0.1707</v>
+      </c>
+      <c r="N2">
+        <v>5</v>
+      </c>
+      <c r="O2">
+        <v>116</v>
+      </c>
+      <c r="P2">
+        <v>4.15</v>
+      </c>
+      <c r="Q2">
+        <v>0.1724</v>
+      </c>
+      <c r="R2">
+        <v>0.367</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V2" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T2">
+        <v>0.2529</v>
+      </c>
+      <c r="U2">
+        <v>0.2629</v>
+      </c>
+      <c r="V2">
+        <v>9</v>
+      </c>
+      <c r="W2">
+        <v>0.2542</v>
+      </c>
+      <c r="X2">
+        <v>0.2245</v>
+      </c>
+      <c r="Y2">
+        <v>1.0317</v>
       </c>
       <c r="AA2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC2" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD2">
+        <v>4.67</v>
       </c>
       <c r="AE2" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="AF2">
+        <v>0.1713</v>
+      </c>
+      <c r="AG2">
+        <v>1.1264</v>
+      </c>
+      <c r="AH2">
+        <v>0.16</v>
+      </c>
+      <c r="AM2">
+        <v>4.83</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -805,28 +865,28 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-115</v>
+        <v>122</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>-156</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G3">
-        <v>822939</v>
+        <v>824478</v>
       </c>
       <c r="H3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -835,70 +895,70 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>0.2225</v>
+        <v>0.182</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="P3">
-        <v>4.13</v>
+        <v>4.48</v>
       </c>
       <c r="Q3">
+        <v>0.1698</v>
+      </c>
+      <c r="R3">
+        <v>0.346</v>
+      </c>
+      <c r="S3" t="s">
+        <v>43</v>
+      </c>
+      <c r="T3">
+        <v>0.1968</v>
+      </c>
+      <c r="U3">
         <v>0.1856</v>
       </c>
-      <c r="R3">
-        <v>0.327</v>
-      </c>
-      <c r="S3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T3">
-        <v>0.2848</v>
-      </c>
-      <c r="U3">
-        <v>0.2531</v>
-      </c>
       <c r="V3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W3">
-        <v>0.2564</v>
+        <v>0.2124</v>
       </c>
       <c r="X3">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y3">
-        <v>1.0211</v>
+        <v>0.9658</v>
       </c>
       <c r="AA3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD3">
-        <v>5.59</v>
+        <v>3.27</v>
       </c>
       <c r="AE3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2104</v>
+        <v>0.1778</v>
       </c>
       <c r="AG3">
-        <v>1.2717</v>
+        <v>0.8765</v>
       </c>
       <c r="AH3">
         <v>0.16</v>
       </c>
       <c r="AM3">
-        <v>5.75</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -906,7 +966,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -918,13 +978,13 @@
         <v>115</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>822939</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I4">
         <v>5.7</v>
@@ -957,13 +1017,13 @@
         <v>0.383</v>
       </c>
       <c r="S4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="T4">
-        <v>0.1804</v>
+        <v>0.1805</v>
       </c>
       <c r="U4">
-        <v>0.1772</v>
+        <v>0.1766</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -972,34 +1032,34 @@
         <v>0.1892</v>
       </c>
       <c r="X4">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y4">
-        <v>0.9068</v>
+        <v>0.88</v>
       </c>
       <c r="AA4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="AE4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF4">
         <v>0.1981</v>
       </c>
       <c r="AG4">
-        <v>0.8054</v>
+        <v>0.8038</v>
       </c>
       <c r="AH4">
         <v>0.16</v>
       </c>
       <c r="AM4">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1007,43 +1067,100 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D5">
-        <v>-128</v>
+        <v>-115</v>
       </c>
       <c r="E5">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G5" t="s">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="G5">
+        <v>822939</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="b">
+        <v>0</v>
+      </c>
       <c r="L5">
         <v>6</v>
       </c>
+      <c r="M5">
+        <v>0.2225</v>
+      </c>
+      <c r="N5">
+        <v>5</v>
+      </c>
+      <c r="O5">
+        <v>97</v>
+      </c>
+      <c r="P5">
+        <v>4.13</v>
+      </c>
+      <c r="Q5">
+        <v>0.1856</v>
+      </c>
+      <c r="R5">
+        <v>0.327</v>
+      </c>
       <c r="S5" t="s">
-        <v>42</v>
-      </c>
-      <c r="V5" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T5">
+        <v>0.2848</v>
+      </c>
+      <c r="U5">
+        <v>0.2531</v>
+      </c>
+      <c r="V5">
+        <v>9</v>
+      </c>
+      <c r="W5">
+        <v>0.2564</v>
+      </c>
+      <c r="X5">
+        <v>0.2245</v>
+      </c>
+      <c r="Y5">
+        <v>1.0211</v>
       </c>
       <c r="AA5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC5" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD5">
+        <v>5.57</v>
       </c>
       <c r="AE5" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="AF5">
+        <v>0.2104</v>
+      </c>
+      <c r="AG5">
+        <v>1.2683</v>
+      </c>
+      <c r="AH5">
+        <v>0.16</v>
+      </c>
+      <c r="AM5">
+        <v>5.73</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1063,13 +1180,13 @@
         <v>-155</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>823427</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I6">
         <v>5.2</v>
@@ -1102,7 +1219,7 @@
         <v>0.327</v>
       </c>
       <c r="S6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="T6">
         <v>0.1805</v>
@@ -1117,34 +1234,34 @@
         <v>0.2246</v>
       </c>
       <c r="X6">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y6">
-        <v>0.9677</v>
+        <v>0.9355</v>
       </c>
       <c r="AA6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD6">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="AE6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF6">
         <v>0.1694</v>
       </c>
       <c r="AG6">
-        <v>0.8059</v>
+        <v>0.8037</v>
       </c>
       <c r="AH6">
         <v>0.16</v>
       </c>
       <c r="AM6">
-        <v>3.06</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1152,28 +1269,19 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" t="s">
         <v>52</v>
       </c>
-      <c r="C7">
-        <v>4.5</v>
-      </c>
-      <c r="D7">
-        <v>-108</v>
-      </c>
-      <c r="E7">
-        <v>-115</v>
-      </c>
-      <c r="F7" t="s">
-        <v>41</v>
-      </c>
       <c r="G7">
-        <v>824478</v>
+        <v>823427</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I7">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
@@ -1182,70 +1290,70 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>0.1707</v>
+        <v>0.2802</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="P7">
         <v>4.15</v>
       </c>
       <c r="Q7">
-        <v>0.1724</v>
+        <v>0.3058</v>
       </c>
       <c r="R7">
-        <v>0.367</v>
+        <v>0.377</v>
       </c>
       <c r="S7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2529</v>
+        <v>0.2386</v>
       </c>
       <c r="U7">
-        <v>0.2629</v>
+        <v>0.2292</v>
       </c>
       <c r="V7">
         <v>9</v>
       </c>
       <c r="W7">
-        <v>0.2542</v>
+        <v>0.2314</v>
       </c>
       <c r="X7">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y7">
-        <v>1.0317</v>
+        <v>1.0337</v>
       </c>
       <c r="AA7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.68</v>
+        <v>8.23</v>
       </c>
       <c r="AE7" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AF7">
-        <v>0.1713</v>
+        <v>0.2898</v>
       </c>
       <c r="AG7">
-        <v>1.1294</v>
+        <v>1.0628</v>
       </c>
       <c r="AH7">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.84</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1253,28 +1361,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>-156</v>
+        <v>-143</v>
       </c>
       <c r="F8" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>824478</v>
+        <v>823343</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I8">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1283,70 +1391,70 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>0.182</v>
+        <v>0.1806</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="P8">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="Q8">
-        <v>0.1698</v>
+        <v>0.161</v>
       </c>
       <c r="R8">
-        <v>0.346</v>
+        <v>0.371</v>
       </c>
       <c r="S8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.1968</v>
+        <v>0.2135</v>
       </c>
       <c r="U8">
-        <v>0.1856</v>
+        <v>0.2374</v>
       </c>
       <c r="V8">
         <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2124</v>
+        <v>0.2552</v>
       </c>
       <c r="X8">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y8">
-        <v>0.9658</v>
+        <v>1.0441</v>
       </c>
       <c r="AA8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.28</v>
+        <v>4.21</v>
       </c>
       <c r="AE8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF8">
-        <v>0.1778</v>
+        <v>0.1733</v>
       </c>
       <c r="AG8">
-        <v>0.8788</v>
+        <v>0.9508</v>
       </c>
       <c r="AH8">
         <v>0.16</v>
       </c>
       <c r="AM8">
-        <v>3.44</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1354,7 +1462,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C9">
         <v>2.5</v>
@@ -1366,13 +1474,13 @@
         <v>133</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>823343</v>
       </c>
       <c r="H9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I9">
         <v>4.5</v>
@@ -1405,7 +1513,7 @@
         <v>0.322</v>
       </c>
       <c r="S9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T9">
         <v>0.187</v>
@@ -1420,34 +1528,34 @@
         <v>0.2248</v>
       </c>
       <c r="X9">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y9">
         <v>0.9826</v>
       </c>
       <c r="AA9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD9">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AE9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF9">
         <v>0.1531</v>
       </c>
       <c r="AG9">
-        <v>0.8351</v>
+        <v>0.8328</v>
       </c>
       <c r="AH9">
         <v>0.16</v>
       </c>
       <c r="AM9">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1455,28 +1563,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D10">
-        <v>116</v>
+        <v>-142</v>
       </c>
       <c r="E10">
-        <v>-143</v>
+        <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>823343</v>
+        <v>824725</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I10">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1488,67 +1596,67 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>0.1806</v>
+        <v>0.1748</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P10">
-        <v>4.41</v>
+        <v>4.25</v>
       </c>
       <c r="Q10">
-        <v>0.161</v>
+        <v>0.1913</v>
       </c>
       <c r="R10">
-        <v>0.371</v>
+        <v>0.365</v>
       </c>
       <c r="S10" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2135</v>
+        <v>0.2109</v>
       </c>
       <c r="U10">
-        <v>0.2374</v>
+        <v>0.1979</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2552</v>
+        <v>0.2169</v>
       </c>
       <c r="X10">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y10">
-        <v>1.0441</v>
+        <v>0.9913</v>
       </c>
       <c r="AA10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.22</v>
+        <v>3.44</v>
       </c>
       <c r="AE10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.1733</v>
+        <v>0.1808</v>
       </c>
       <c r="AG10">
-        <v>0.9533</v>
+        <v>0.9394</v>
       </c>
       <c r="AH10">
         <v>0.16</v>
       </c>
       <c r="AM10">
-        <v>4.38</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1556,100 +1664,79 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11">
-        <v>3.5</v>
-      </c>
-      <c r="D11">
-        <v>-142</v>
-      </c>
-      <c r="E11">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>824725</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="I11">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="b">
         <v>0</v>
       </c>
       <c r="L11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>0.1748</v>
-      </c>
-      <c r="N11">
-        <v>5</v>
-      </c>
-      <c r="O11">
-        <v>115</v>
+        <v>0.1765</v>
       </c>
       <c r="P11">
-        <v>4.25</v>
-      </c>
-      <c r="Q11">
-        <v>0.1913</v>
-      </c>
-      <c r="R11">
-        <v>0.365</v>
+        <v>4</v>
       </c>
       <c r="S11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.2109</v>
+        <v>0.1775</v>
       </c>
       <c r="U11">
-        <v>0.1979</v>
+        <v>0.1778</v>
       </c>
       <c r="V11">
         <v>9</v>
       </c>
       <c r="W11">
-        <v>0.2169</v>
+        <v>0.1745</v>
       </c>
       <c r="X11">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y11">
-        <v>0.9913</v>
+        <v>0.912</v>
       </c>
       <c r="AA11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD11">
-        <v>3.45</v>
+        <v>2.29</v>
       </c>
       <c r="AE11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF11">
-        <v>0.1808</v>
+        <v>0.1765</v>
       </c>
       <c r="AG11">
-        <v>0.9419</v>
+        <v>0.7906</v>
       </c>
       <c r="AH11">
         <v>0.16</v>
       </c>
       <c r="AM11">
-        <v>3.61</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1657,7 +1744,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>3.5</v>
@@ -1669,13 +1756,13 @@
         <v>125</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>823589</v>
       </c>
       <c r="H12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I12">
         <v>4.8</v>
@@ -1708,13 +1795,13 @@
         <v>0.353</v>
       </c>
       <c r="S12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="T12">
-        <v>0.2494</v>
+        <v>0.2625</v>
       </c>
       <c r="U12">
-        <v>0.2434</v>
+        <v>0.2538</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1723,34 +1810,34 @@
         <v>0.225</v>
       </c>
       <c r="X12">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y12">
-        <v>0.9812</v>
+        <v>0.9654</v>
       </c>
       <c r="AA12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.34</v>
+        <v>4.48</v>
       </c>
       <c r="AE12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF12">
         <v>0.1917</v>
       </c>
       <c r="AG12">
-        <v>1.1137</v>
+        <v>1.169</v>
       </c>
       <c r="AH12">
         <v>0.16</v>
       </c>
       <c r="AM12">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1758,7 +1845,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -1770,13 +1857,13 @@
         <v>120</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>823589</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I13">
         <v>5.7</v>
@@ -1809,7 +1896,7 @@
         <v>0.375</v>
       </c>
       <c r="S13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T13">
         <v>0.1541</v>
@@ -1824,34 +1911,34 @@
         <v>0.2171</v>
       </c>
       <c r="X13">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y13">
         <v>0.9938</v>
       </c>
       <c r="AA13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC13" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.55</v>
+        <v>4.54</v>
       </c>
       <c r="AE13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF13">
         <v>0.2812</v>
       </c>
       <c r="AG13">
-        <v>0.6883</v>
+        <v>0.6865</v>
       </c>
       <c r="AH13">
         <v>0.16</v>
       </c>
       <c r="AM13">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1859,28 +1946,28 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D14">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E14">
-        <v>-125</v>
+        <v>-139</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>824077</v>
       </c>
       <c r="H14" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I14">
-        <v>6.3</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1892,67 +1979,67 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1912</v>
+        <v>0.2156</v>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O14">
-        <v>125</v>
+        <v>62</v>
       </c>
       <c r="P14">
-        <v>4.06</v>
+        <v>4.39</v>
       </c>
       <c r="Q14">
-        <v>0.168</v>
+        <v>0.2097</v>
       </c>
       <c r="R14">
-        <v>0.385</v>
+        <v>0.237</v>
       </c>
       <c r="S14" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2534</v>
+        <v>0.2083</v>
       </c>
       <c r="U14">
-        <v>0.2192</v>
+        <v>0.2106</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>0.2153</v>
+        <v>0.2103</v>
       </c>
       <c r="X14">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y14">
-        <v>1.0228</v>
+        <v>0.9716</v>
       </c>
       <c r="AA14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD14">
-        <v>5.38</v>
+        <v>3.77</v>
       </c>
       <c r="AE14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF14">
-        <v>0.1823</v>
+        <v>0.2142</v>
       </c>
       <c r="AG14">
-        <v>1.1315</v>
+        <v>0.9275</v>
       </c>
       <c r="AH14">
         <v>0.16</v>
       </c>
       <c r="AM14">
-        <v>5.54</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -1960,28 +2047,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C15">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D15">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E15">
-        <v>-139</v>
+        <v>-125</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>824077</v>
       </c>
       <c r="H15" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="I15">
-        <v>4.4</v>
+        <v>6.3</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -1993,67 +2080,67 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2156</v>
+        <v>0.1912</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>62</v>
+        <v>125</v>
       </c>
       <c r="P15">
-        <v>4.39</v>
+        <v>4.06</v>
       </c>
       <c r="Q15">
-        <v>0.2097</v>
+        <v>0.168</v>
       </c>
       <c r="R15">
-        <v>0.237</v>
+        <v>0.385</v>
       </c>
       <c r="S15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2083</v>
+        <v>0.2534</v>
       </c>
       <c r="U15">
-        <v>0.2106</v>
+        <v>0.2192</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2103</v>
+        <v>0.2153</v>
       </c>
       <c r="X15">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y15">
-        <v>0.9716</v>
+        <v>1.0228</v>
       </c>
       <c r="AA15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC15" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD15">
-        <v>3.78</v>
+        <v>5.36</v>
       </c>
       <c r="AE15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF15">
-        <v>0.2142</v>
+        <v>0.1823</v>
       </c>
       <c r="AG15">
-        <v>0.93</v>
+        <v>1.1285</v>
       </c>
       <c r="AH15">
         <v>0.16</v>
       </c>
       <c r="AM15">
-        <v>3.94</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2061,43 +2148,91 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16">
-        <v>3.5</v>
-      </c>
-      <c r="D16">
-        <v>-104</v>
-      </c>
-      <c r="E16">
-        <v>-109</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" t="s">
-        <v>42</v>
+        <v>70</v>
+      </c>
+      <c r="G16">
+        <v>823668</v>
       </c>
       <c r="H16" t="s">
         <v>42</v>
       </c>
+      <c r="I16">
+        <v>5.1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
       <c r="L16">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0.186</v>
+      </c>
+      <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="O16">
+        <v>97</v>
+      </c>
+      <c r="P16">
+        <v>4.04</v>
+      </c>
+      <c r="Q16">
+        <v>0.1856</v>
+      </c>
+      <c r="R16">
+        <v>0.327</v>
       </c>
       <c r="S16" t="s">
-        <v>42</v>
-      </c>
-      <c r="V16" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="T16">
+        <v>0.2081</v>
+      </c>
+      <c r="U16">
+        <v>0.2056</v>
+      </c>
+      <c r="V16">
+        <v>9</v>
+      </c>
+      <c r="W16">
+        <v>0.2255</v>
+      </c>
+      <c r="X16">
+        <v>0.2245</v>
+      </c>
+      <c r="Y16">
+        <v>0.9816</v>
       </c>
       <c r="AA16" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC16" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="AD16">
+        <v>3.49</v>
       </c>
       <c r="AE16" t="s">
-        <v>42</v>
+        <v>45</v>
+      </c>
+      <c r="AF16">
+        <v>0.1859</v>
+      </c>
+      <c r="AG16">
+        <v>0.9266</v>
+      </c>
+      <c r="AH16">
+        <v>0.16</v>
+      </c>
+      <c r="AM16">
+        <v>3.65</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2105,7 +2240,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2117,13 +2252,13 @@
         <v>-119</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G17">
         <v>823668</v>
       </c>
       <c r="H17" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I17">
         <v>5.5</v>
@@ -2156,7 +2291,7 @@
         <v>0.365</v>
       </c>
       <c r="S17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T17">
         <v>0.2315</v>
@@ -2171,34 +2306,34 @@
         <v>0.2177</v>
       </c>
       <c r="X17">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y17">
         <v>0.9695</v>
       </c>
       <c r="AA17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC17" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="AE17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF17">
         <v>0.1533</v>
       </c>
       <c r="AG17">
-        <v>1.0339</v>
+        <v>1.0312</v>
       </c>
       <c r="AH17">
         <v>0.16</v>
       </c>
       <c r="AM17">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2206,7 +2341,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2218,13 +2353,13 @@
         <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>824641</v>
       </c>
       <c r="H18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I18">
         <v>5.2</v>
@@ -2257,7 +2392,7 @@
         <v>0.373</v>
       </c>
       <c r="S18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T18">
         <v>0.2302</v>
@@ -2272,34 +2407,34 @@
         <v>0.2179</v>
       </c>
       <c r="X18">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y18">
         <v>0.9619</v>
       </c>
       <c r="AA18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC18" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="AE18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF18">
         <v>0.2061</v>
       </c>
       <c r="AG18">
-        <v>1.0278</v>
+        <v>1.0251</v>
       </c>
       <c r="AH18">
         <v>0.16</v>
       </c>
       <c r="AM18">
-        <v>4.82</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2307,7 +2442,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>5.5</v>
@@ -2319,13 +2454,13 @@
         <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G19">
         <v>824641</v>
       </c>
       <c r="H19" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I19">
         <v>5.7</v>
@@ -2358,7 +2493,7 @@
         <v>0.367</v>
       </c>
       <c r="S19" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T19">
         <v>0.2179</v>
@@ -2373,34 +2508,34 @@
         <v>0.2442</v>
       </c>
       <c r="X19">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y19">
         <v>1.0245</v>
       </c>
       <c r="AA19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="AE19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF19">
         <v>0.2276</v>
       </c>
       <c r="AG19">
-        <v>0.9729</v>
+        <v>0.9703</v>
       </c>
       <c r="AH19">
         <v>0.16</v>
       </c>
       <c r="AM19">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2408,7 +2543,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>2.5</v>
@@ -2420,13 +2555,13 @@
         <v>136</v>
       </c>
       <c r="F20" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G20">
         <v>824320</v>
       </c>
       <c r="H20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="I20">
         <v>5.4</v>
@@ -2459,7 +2594,7 @@
         <v>0.367</v>
       </c>
       <c r="S20" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T20">
         <v>0.2857</v>
@@ -2474,34 +2609,34 @@
         <v>0.2074</v>
       </c>
       <c r="X20">
-        <v>0.2239</v>
+        <v>0.2245</v>
       </c>
       <c r="Y20">
         <v>1.0072</v>
       </c>
       <c r="AA20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="AE20" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AF20">
         <v>0.1451</v>
       </c>
       <c r="AG20">
-        <v>1.2758</v>
+        <v>1.2724</v>
       </c>
       <c r="AH20">
         <v>0.16</v>
       </c>
       <c r="AM20">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2509,43 +2644,43 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C21">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D21">
-        <v>-148</v>
+        <v>-118</v>
       </c>
       <c r="E21">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L21">
         <v>6</v>
       </c>
       <c r="S21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2553,91 +2688,43 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>78</v>
+      </c>
+      <c r="C22">
+        <v>6.5</v>
+      </c>
+      <c r="D22">
+        <v>-128</v>
+      </c>
+      <c r="E22">
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
-      </c>
-      <c r="G22">
-        <v>823427</v>
+        <v>52</v>
+      </c>
+      <c r="G22" t="s">
+        <v>44</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
-      </c>
-      <c r="I22">
-        <v>6.2</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0.2802</v>
-      </c>
-      <c r="N22">
-        <v>5</v>
-      </c>
-      <c r="O22">
-        <v>121</v>
-      </c>
-      <c r="P22">
-        <v>4.15</v>
-      </c>
-      <c r="Q22">
-        <v>0.3058</v>
-      </c>
-      <c r="R22">
-        <v>0.377</v>
+        <v>6</v>
       </c>
       <c r="S22" t="s">
-        <v>46</v>
-      </c>
-      <c r="T22">
-        <v>0.2386</v>
-      </c>
-      <c r="U22">
-        <v>0.2292</v>
-      </c>
-      <c r="V22">
-        <v>9</v>
-      </c>
-      <c r="W22">
-        <v>0.2314</v>
-      </c>
-      <c r="X22">
-        <v>0.2239</v>
-      </c>
-      <c r="Y22">
-        <v>1.0337</v>
+        <v>44</v>
+      </c>
+      <c r="V22" t="s">
+        <v>44</v>
       </c>
       <c r="AA22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC22" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD22">
-        <v>8.25</v>
+        <v>44</v>
       </c>
       <c r="AE22" t="s">
-        <v>76</v>
-      </c>
-      <c r="AF22">
-        <v>0.2898</v>
-      </c>
-      <c r="AG22">
-        <v>1.0656</v>
-      </c>
-      <c r="AH22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>8.25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2645,79 +2732,43 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="C23">
+        <v>3.5</v>
+      </c>
+      <c r="D23">
+        <v>-104</v>
+      </c>
+      <c r="E23">
+        <v>-109</v>
       </c>
       <c r="F23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23">
-        <v>824725</v>
+        <v>70</v>
+      </c>
+      <c r="G23" t="s">
+        <v>44</v>
       </c>
       <c r="H23" t="s">
-        <v>78</v>
-      </c>
-      <c r="I23">
-        <v>4.5</v>
-      </c>
-      <c r="J23" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0.1765</v>
-      </c>
-      <c r="P23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S23" t="s">
-        <v>46</v>
-      </c>
-      <c r="T23">
-        <v>0.1775</v>
-      </c>
-      <c r="U23">
-        <v>0.1778</v>
-      </c>
-      <c r="V23">
-        <v>9</v>
-      </c>
-      <c r="W23">
-        <v>0.1745</v>
-      </c>
-      <c r="X23">
-        <v>0.2239</v>
-      </c>
-      <c r="Y23">
-        <v>0.912</v>
+        <v>44</v>
+      </c>
+      <c r="V23" t="s">
+        <v>44</v>
       </c>
       <c r="AA23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC23" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD23">
-        <v>2.3</v>
+        <v>44</v>
       </c>
       <c r="AE23" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF23">
-        <v>0.1765</v>
-      </c>
-      <c r="AG23">
-        <v>0.7928</v>
-      </c>
-      <c r="AH23">
-        <v>0.16</v>
-      </c>
-      <c r="AM23">
-        <v>2.46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2725,91 +2776,43 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="C24">
+        <v>6.5</v>
+      </c>
+      <c r="D24">
+        <v>-148</v>
+      </c>
+      <c r="E24">
+        <v>117</v>
       </c>
       <c r="F24" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24">
-        <v>823668</v>
+        <v>76</v>
+      </c>
+      <c r="G24" t="s">
+        <v>44</v>
       </c>
       <c r="H24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24">
-        <v>5.1</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0.186</v>
-      </c>
-      <c r="N24">
-        <v>5</v>
-      </c>
-      <c r="O24">
-        <v>97</v>
-      </c>
-      <c r="P24">
-        <v>4.04</v>
-      </c>
-      <c r="Q24">
-        <v>0.1856</v>
-      </c>
-      <c r="R24">
-        <v>0.327</v>
+        <v>6</v>
       </c>
       <c r="S24" t="s">
-        <v>46</v>
-      </c>
-      <c r="T24">
-        <v>0.2081</v>
-      </c>
-      <c r="U24">
-        <v>0.2056</v>
-      </c>
-      <c r="V24">
-        <v>9</v>
-      </c>
-      <c r="W24">
-        <v>0.2255</v>
-      </c>
-      <c r="X24">
-        <v>0.2239</v>
-      </c>
-      <c r="Y24">
-        <v>0.9816</v>
+        <v>44</v>
+      </c>
+      <c r="V24" t="s">
+        <v>44</v>
       </c>
       <c r="AA24" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AC24" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD24">
-        <v>3.5</v>
+        <v>44</v>
       </c>
       <c r="AE24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF24">
-        <v>0.1859</v>
-      </c>
-      <c r="AG24">
-        <v>0.9291</v>
-      </c>
-      <c r="AH24">
-        <v>0.16</v>
-      </c>
-      <c r="AM24">
-        <v>3.66</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-17.xlsx
+++ b/data/k-props/2026-08-17.xlsx
@@ -142,64 +142,64 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Shane McClanahan</t>
+  </si>
+  <si>
+    <t>Janson Junk</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Cristopher Sánchez</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Framber Valdez</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Carmen Mlodzinski</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Mitch Bratt</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Alec Gamboa</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>Shane McClanahan</t>
-  </si>
-  <si>
-    <t>Janson Junk</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>Cristopher Sánchez</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Framber Valdez</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Carmen Mlodzinski</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Mitch Bratt</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Alec Gamboa</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
   </si>
   <si>
     <t>Walker Buehler</t>
@@ -818,22 +818,22 @@
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2529</v>
+        <v>0.2728</v>
       </c>
       <c r="U2">
-        <v>0.2629</v>
+        <v>0.2663</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2542</v>
+        <v>0.2553</v>
       </c>
       <c r="X2">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y2">
-        <v>1.0317</v>
+        <v>1.068</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -842,7 +842,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.67</v>
+        <v>5.22</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -851,13 +851,13 @@
         <v>0.1713</v>
       </c>
       <c r="AG2">
-        <v>1.1264</v>
+        <v>1.2173</v>
       </c>
       <c r="AH2">
         <v>0.16</v>
       </c>
       <c r="AM2">
-        <v>4.83</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -919,22 +919,22 @@
         <v>43</v>
       </c>
       <c r="T3">
-        <v>0.1968</v>
+        <v>0.2029</v>
       </c>
       <c r="U3">
-        <v>0.1856</v>
+        <v>0.1901</v>
       </c>
       <c r="V3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2124</v>
+        <v>0.2129</v>
       </c>
       <c r="X3">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y3">
-        <v>0.9658</v>
+        <v>0.9246</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -943,7 +943,7 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
@@ -952,13 +952,13 @@
         <v>0.1778</v>
       </c>
       <c r="AG3">
-        <v>0.8765</v>
+        <v>0.9054</v>
       </c>
       <c r="AH3">
         <v>0.16</v>
       </c>
       <c r="AM3">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1017,7 +1017,7 @@
         <v>0.383</v>
       </c>
       <c r="S4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T4">
         <v>0.1805</v>
@@ -1032,7 +1032,7 @@
         <v>0.1892</v>
       </c>
       <c r="X4">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y4">
         <v>0.88</v>
@@ -1044,7 +1044,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="AE4" t="s">
         <v>45</v>
@@ -1053,13 +1053,13 @@
         <v>0.1981</v>
       </c>
       <c r="AG4">
-        <v>0.8038</v>
+        <v>0.8054</v>
       </c>
       <c r="AH4">
         <v>0.16</v>
       </c>
       <c r="AM4">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1067,7 +1067,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1121,10 +1121,10 @@
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2848</v>
+        <v>0.2586</v>
       </c>
       <c r="U5">
-        <v>0.2531</v>
+        <v>0.2485</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1133,10 +1133,10 @@
         <v>0.2564</v>
       </c>
       <c r="X5">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y5">
-        <v>1.0211</v>
+        <v>1.0638</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1145,7 +1145,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>5.57</v>
+        <v>5.28</v>
       </c>
       <c r="AE5" t="s">
         <v>45</v>
@@ -1154,13 +1154,13 @@
         <v>0.2104</v>
       </c>
       <c r="AG5">
-        <v>1.2683</v>
+        <v>1.154</v>
       </c>
       <c r="AH5">
         <v>0.16</v>
       </c>
       <c r="AM5">
-        <v>5.73</v>
+        <v>5.44</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1168,7 +1168,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1180,7 +1180,7 @@
         <v>-155</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>823427</v>
@@ -1219,7 +1219,7 @@
         <v>0.327</v>
       </c>
       <c r="S6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T6">
         <v>0.1805</v>
@@ -1234,7 +1234,7 @@
         <v>0.2246</v>
       </c>
       <c r="X6">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y6">
         <v>0.9355</v>
@@ -1246,7 +1246,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1255,13 +1255,13 @@
         <v>0.1694</v>
       </c>
       <c r="AG6">
-        <v>0.8037</v>
+        <v>0.8054</v>
       </c>
       <c r="AH6">
         <v>0.16</v>
       </c>
       <c r="AM6">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1269,10 +1269,10 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>823427</v>
@@ -1314,10 +1314,10 @@
         <v>43</v>
       </c>
       <c r="T7">
-        <v>0.2386</v>
+        <v>0.2455</v>
       </c>
       <c r="U7">
-        <v>0.2292</v>
+        <v>0.2217</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1326,10 +1326,10 @@
         <v>0.2314</v>
       </c>
       <c r="X7">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y7">
-        <v>1.0337</v>
+        <v>1.0099</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1338,22 +1338,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>8.23</v>
+        <v>8.29</v>
       </c>
       <c r="AE7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AF7">
         <v>0.2898</v>
       </c>
       <c r="AG7">
-        <v>1.0628</v>
+        <v>1.0957</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>8.23</v>
+        <v>8.29</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1361,7 +1361,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8">
         <v>5.5</v>
@@ -1373,7 +1373,7 @@
         <v>-143</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>823343</v>
@@ -1415,22 +1415,22 @@
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2135</v>
+        <v>0.2644</v>
       </c>
       <c r="U8">
-        <v>0.2374</v>
+        <v>0.2701</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
         <v>0.2552</v>
       </c>
       <c r="X8">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y8">
-        <v>1.0441</v>
+        <v>1.1071</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1439,7 +1439,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>4.21</v>
+        <v>5.54</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1448,13 +1448,13 @@
         <v>0.1733</v>
       </c>
       <c r="AG8">
-        <v>0.9508</v>
+        <v>1.1798</v>
       </c>
       <c r="AH8">
         <v>0.16</v>
       </c>
       <c r="AM8">
-        <v>4.37</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1462,7 +1462,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9">
         <v>2.5</v>
@@ -1474,13 +1474,13 @@
         <v>133</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9">
         <v>823343</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I9">
         <v>4.5</v>
@@ -1516,10 +1516,10 @@
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.187</v>
+        <v>0.2181</v>
       </c>
       <c r="U9">
-        <v>0.1952</v>
+        <v>0.1854</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1528,10 +1528,10 @@
         <v>0.2248</v>
       </c>
       <c r="X9">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y9">
-        <v>0.9826</v>
+        <v>0.88</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1540,7 +1540,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1549,13 +1549,13 @@
         <v>0.1531</v>
       </c>
       <c r="AG9">
-        <v>0.8328</v>
+        <v>0.9734</v>
       </c>
       <c r="AH9">
         <v>0.16</v>
       </c>
       <c r="AM9">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1575,7 +1575,7 @@
         <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10">
         <v>824725</v>
@@ -1617,22 +1617,22 @@
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2109</v>
+        <v>0.2232</v>
       </c>
       <c r="U10">
-        <v>0.1979</v>
+        <v>0.2049</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>0.2169</v>
       </c>
       <c r="X10">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y10">
-        <v>0.9913</v>
+        <v>0.9787</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1641,7 +1641,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1650,13 +1650,13 @@
         <v>0.1808</v>
       </c>
       <c r="AG10">
-        <v>0.9394</v>
+        <v>0.9962</v>
       </c>
       <c r="AH10">
         <v>0.16</v>
       </c>
       <c r="AM10">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1664,16 +1664,16 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>824725</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I11">
         <v>4.5</v>
@@ -1694,7 +1694,7 @@
         <v>4</v>
       </c>
       <c r="S11" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="T11">
         <v>0.1775</v>
@@ -1709,7 +1709,7 @@
         <v>0.1745</v>
       </c>
       <c r="X11">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y11">
         <v>0.912</v>
@@ -1721,7 +1721,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
@@ -1730,13 +1730,13 @@
         <v>0.1765</v>
       </c>
       <c r="AG11">
-        <v>0.7906</v>
+        <v>0.7923</v>
       </c>
       <c r="AH11">
         <v>0.16</v>
       </c>
       <c r="AM11">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1795,7 +1795,7 @@
         <v>0.353</v>
       </c>
       <c r="S12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T12">
         <v>0.2625</v>
@@ -1810,7 +1810,7 @@
         <v>0.225</v>
       </c>
       <c r="X12">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y12">
         <v>0.9654</v>
@@ -1822,7 +1822,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>4.48</v>
+        <v>4.49</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1831,13 +1831,13 @@
         <v>0.1917</v>
       </c>
       <c r="AG12">
-        <v>1.169</v>
+        <v>1.1714</v>
       </c>
       <c r="AH12">
         <v>0.16</v>
       </c>
       <c r="AM12">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1899,10 +1899,10 @@
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.1541</v>
+        <v>0.1737</v>
       </c>
       <c r="U13">
-        <v>0.1718</v>
+        <v>0.1746</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1911,10 +1911,10 @@
         <v>0.2171</v>
       </c>
       <c r="X13">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y13">
-        <v>0.9938</v>
+        <v>1.0012</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1923,7 +1923,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.54</v>
+        <v>5.17</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1932,13 +1932,13 @@
         <v>0.2812</v>
       </c>
       <c r="AG13">
-        <v>0.6865</v>
+        <v>0.7754</v>
       </c>
       <c r="AH13">
         <v>0.16</v>
       </c>
       <c r="AM13">
-        <v>4.7</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1964,7 +1964,7 @@
         <v>824077</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I14">
         <v>4.4</v>
@@ -2000,10 +2000,10 @@
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2083</v>
+        <v>0.2087</v>
       </c>
       <c r="U14">
-        <v>0.2106</v>
+        <v>0.2117</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -2012,10 +2012,10 @@
         <v>0.2103</v>
       </c>
       <c r="X14">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y14">
-        <v>0.9716</v>
+        <v>0.9548</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2024,7 +2024,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2033,13 +2033,13 @@
         <v>0.2142</v>
       </c>
       <c r="AG14">
-        <v>0.9275</v>
+        <v>0.9316</v>
       </c>
       <c r="AH14">
         <v>0.16</v>
       </c>
       <c r="AM14">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2101,10 +2101,10 @@
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2534</v>
+        <v>0.1859</v>
       </c>
       <c r="U15">
-        <v>0.2192</v>
+        <v>0.1818</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -2113,10 +2113,10 @@
         <v>0.2153</v>
       </c>
       <c r="X15">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y15">
-        <v>1.0228</v>
+        <v>0.9819</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2125,7 +2125,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.36</v>
+        <v>3.79</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2134,13 +2134,13 @@
         <v>0.1823</v>
       </c>
       <c r="AG15">
-        <v>1.1285</v>
+        <v>0.8294</v>
       </c>
       <c r="AH15">
         <v>0.16</v>
       </c>
       <c r="AM15">
-        <v>5.52</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2193,10 +2193,10 @@
         <v>43</v>
       </c>
       <c r="T16">
-        <v>0.2081</v>
+        <v>0.2092</v>
       </c>
       <c r="U16">
-        <v>0.2056</v>
+        <v>0.2029</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -2205,10 +2205,10 @@
         <v>0.2255</v>
       </c>
       <c r="X16">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y16">
-        <v>0.9816</v>
+        <v>0.9396</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2217,7 +2217,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>3.49</v>
+        <v>3.37</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2226,13 +2226,13 @@
         <v>0.1859</v>
       </c>
       <c r="AG16">
-        <v>0.9266</v>
+        <v>0.9338</v>
       </c>
       <c r="AH16">
         <v>0.16</v>
       </c>
       <c r="AM16">
-        <v>3.65</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2294,10 +2294,10 @@
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2315</v>
+        <v>0.2149</v>
       </c>
       <c r="U17">
-        <v>0.2236</v>
+        <v>0.2109</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2306,10 +2306,10 @@
         <v>0.2177</v>
       </c>
       <c r="X17">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y17">
-        <v>0.9695</v>
+        <v>0.9357</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2318,7 +2318,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>3.53</v>
+        <v>3.17</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2327,13 +2327,13 @@
         <v>0.1533</v>
       </c>
       <c r="AG17">
-        <v>1.0312</v>
+        <v>0.9593</v>
       </c>
       <c r="AH17">
         <v>0.16</v>
       </c>
       <c r="AM17">
-        <v>3.69</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2392,7 +2392,7 @@
         <v>0.373</v>
       </c>
       <c r="S18" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="T18">
         <v>0.2302</v>
@@ -2407,7 +2407,7 @@
         <v>0.2179</v>
       </c>
       <c r="X18">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y18">
         <v>0.9619</v>
@@ -2419,7 +2419,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2428,13 +2428,13 @@
         <v>0.2061</v>
       </c>
       <c r="AG18">
-        <v>1.0251</v>
+        <v>1.0272</v>
       </c>
       <c r="AH18">
         <v>0.16</v>
       </c>
       <c r="AM18">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2496,10 +2496,10 @@
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2179</v>
+        <v>0.2332</v>
       </c>
       <c r="U19">
-        <v>0.2366</v>
+        <v>0.232</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2508,10 +2508,10 @@
         <v>0.2442</v>
       </c>
       <c r="X19">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y19">
-        <v>1.0245</v>
+        <v>0.9688</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2520,7 +2520,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2529,13 +2529,13 @@
         <v>0.2276</v>
       </c>
       <c r="AG19">
-        <v>0.9703</v>
+        <v>1.0405</v>
       </c>
       <c r="AH19">
         <v>0.16</v>
       </c>
       <c r="AM19">
-        <v>5.38</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2597,10 +2597,10 @@
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2857</v>
+        <v>0.2037</v>
       </c>
       <c r="U20">
-        <v>0.2224</v>
+        <v>0.2072</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2609,10 +2609,10 @@
         <v>0.2074</v>
       </c>
       <c r="X20">
-        <v>0.2245</v>
+        <v>0.2241</v>
       </c>
       <c r="Y20">
-        <v>1.0072</v>
+        <v>0.9901</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2621,7 +2621,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2630,13 +2630,13 @@
         <v>0.1451</v>
       </c>
       <c r="AG20">
-        <v>1.2724</v>
+        <v>0.9091</v>
       </c>
       <c r="AH20">
         <v>0.16</v>
       </c>
       <c r="AM20">
-        <v>4.36</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2700,7 +2700,7 @@
         <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-17.xlsx
+++ b/data/k-props/2026-08-17.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="85">
   <si>
     <t>date</t>
   </si>
@@ -145,19 +145,31 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Rhett Lowder</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Brandon Young</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
     <t/>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Rhett Lowder</t>
-  </si>
-  <si>
-    <t>Brandon Young</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
   </si>
   <si>
     <t>Shane McClanahan</t>
@@ -835,17 +847,23 @@
       <c r="Y2">
         <v>1.068</v>
       </c>
+      <c r="Z2">
+        <v>5</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>0.88</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>5.22</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.1713</v>
@@ -855,6 +873,18 @@
       </c>
       <c r="AH2">
         <v>0.16</v>
+      </c>
+      <c r="AI2">
+        <v>-0.22</v>
+      </c>
+      <c r="AJ2">
+        <v>0.22</v>
+      </c>
+      <c r="AK2">
+        <v>-0.38</v>
+      </c>
+      <c r="AL2">
+        <v>0.38</v>
       </c>
       <c r="AM2">
         <v>5.38</v>
@@ -865,7 +895,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>4.5</v>
@@ -936,17 +966,23 @@
       <c r="Y3">
         <v>0.9246</v>
       </c>
+      <c r="Z3">
+        <v>5</v>
+      </c>
       <c r="AA3" t="s">
         <v>44</v>
       </c>
+      <c r="AB3">
+        <v>-1.1</v>
+      </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD3">
         <v>3.24</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.1778</v>
@@ -956,6 +992,18 @@
       </c>
       <c r="AH3">
         <v>0.16</v>
+      </c>
+      <c r="AI3">
+        <v>1.76</v>
+      </c>
+      <c r="AJ3">
+        <v>1.76</v>
+      </c>
+      <c r="AK3">
+        <v>1.6</v>
+      </c>
+      <c r="AL3">
+        <v>1.6</v>
       </c>
       <c r="AM3">
         <v>3.4</v>
@@ -966,7 +1014,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>3.5</v>
@@ -978,7 +1026,7 @@
         <v>115</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>822939</v>
@@ -1037,17 +1085,23 @@
       <c r="Y4">
         <v>0.88</v>
       </c>
+      <c r="Z4">
+        <v>3</v>
+      </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB4">
+        <v>0.08</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD4">
         <v>3.42</v>
       </c>
       <c r="AE4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF4">
         <v>0.1981</v>
@@ -1057,6 +1111,18 @@
       </c>
       <c r="AH4">
         <v>0.16</v>
+      </c>
+      <c r="AI4">
+        <v>-0.42</v>
+      </c>
+      <c r="AJ4">
+        <v>0.42</v>
+      </c>
+      <c r="AK4">
+        <v>-0.58</v>
+      </c>
+      <c r="AL4">
+        <v>0.58</v>
       </c>
       <c r="AM4">
         <v>3.58</v>
@@ -1067,7 +1133,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>4.5</v>
@@ -1079,7 +1145,7 @@
         <v>100</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>822939</v>
@@ -1138,17 +1204,23 @@
       <c r="Y5">
         <v>1.0638</v>
       </c>
+      <c r="Z5">
+        <v>3</v>
+      </c>
       <c r="AA5" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB5">
+        <v>0.94</v>
       </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AD5">
         <v>5.28</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>0.2104</v>
@@ -1158,6 +1230,18 @@
       </c>
       <c r="AH5">
         <v>0.16</v>
+      </c>
+      <c r="AI5">
+        <v>-2.28</v>
+      </c>
+      <c r="AJ5">
+        <v>2.28</v>
+      </c>
+      <c r="AK5">
+        <v>-2.44</v>
+      </c>
+      <c r="AL5">
+        <v>2.44</v>
       </c>
       <c r="AM5">
         <v>5.44</v>
@@ -1168,7 +1252,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1180,7 +1264,7 @@
         <v>-155</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>823427</v>
@@ -1239,17 +1323,23 @@
       <c r="Y6">
         <v>0.9355</v>
       </c>
+      <c r="Z6">
+        <v>2</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB6">
+        <v>-0.54</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD6">
         <v>2.8</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>0.1694</v>
@@ -1259,6 +1349,18 @@
       </c>
       <c r="AH6">
         <v>0.16</v>
+      </c>
+      <c r="AI6">
+        <v>-0.8</v>
+      </c>
+      <c r="AJ6">
+        <v>0.8</v>
+      </c>
+      <c r="AK6">
+        <v>-0.96</v>
+      </c>
+      <c r="AL6">
+        <v>0.96</v>
       </c>
       <c r="AM6">
         <v>2.96</v>
@@ -1269,10 +1371,10 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>823427</v>
@@ -1332,16 +1434,16 @@
         <v>1.0099</v>
       </c>
       <c r="AA7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD7">
         <v>8.29</v>
       </c>
       <c r="AE7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AF7">
         <v>0.2898</v>
@@ -1361,7 +1463,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>5.5</v>
@@ -1373,7 +1475,7 @@
         <v>-143</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>823343</v>
@@ -1432,17 +1534,23 @@
       <c r="Y8">
         <v>1.1071</v>
       </c>
+      <c r="Z8">
+        <v>5</v>
+      </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB8">
+        <v>0.2</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD8">
         <v>5.54</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.1733</v>
@@ -1452,6 +1560,18 @@
       </c>
       <c r="AH8">
         <v>0.16</v>
+      </c>
+      <c r="AI8">
+        <v>-0.54</v>
+      </c>
+      <c r="AJ8">
+        <v>0.54</v>
+      </c>
+      <c r="AK8">
+        <v>-0.7</v>
+      </c>
+      <c r="AL8">
+        <v>0.7</v>
       </c>
       <c r="AM8">
         <v>5.7</v>
@@ -1462,7 +1582,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>2.5</v>
@@ -1474,13 +1594,13 @@
         <v>133</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>823343</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I9">
         <v>4.5</v>
@@ -1533,17 +1653,23 @@
       <c r="Y9">
         <v>0.88</v>
       </c>
+      <c r="Z9">
+        <v>3</v>
+      </c>
       <c r="AA9" t="s">
         <v>44</v>
       </c>
+      <c r="AB9">
+        <v>0.22</v>
+      </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD9">
         <v>2.56</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.1531</v>
@@ -1553,6 +1679,18 @@
       </c>
       <c r="AH9">
         <v>0.16</v>
+      </c>
+      <c r="AI9">
+        <v>0.44</v>
+      </c>
+      <c r="AJ9">
+        <v>0.44</v>
+      </c>
+      <c r="AK9">
+        <v>0.28</v>
+      </c>
+      <c r="AL9">
+        <v>0.28</v>
       </c>
       <c r="AM9">
         <v>2.72</v>
@@ -1563,7 +1701,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1575,7 +1713,7 @@
         <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G10">
         <v>824725</v>
@@ -1634,17 +1772,23 @@
       <c r="Y10">
         <v>0.9787</v>
       </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB10">
+        <v>0.26</v>
       </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD10">
         <v>3.6</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.1808</v>
@@ -1654,6 +1798,18 @@
       </c>
       <c r="AH10">
         <v>0.16</v>
+      </c>
+      <c r="AI10">
+        <v>-3.6</v>
+      </c>
+      <c r="AJ10">
+        <v>3.6</v>
+      </c>
+      <c r="AK10">
+        <v>-3.76</v>
+      </c>
+      <c r="AL10">
+        <v>3.76</v>
       </c>
       <c r="AM10">
         <v>3.76</v>
@@ -1664,16 +1820,16 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G11">
         <v>824725</v>
       </c>
       <c r="H11" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="I11">
         <v>4.5</v>
@@ -1694,7 +1850,7 @@
         <v>4</v>
       </c>
       <c r="S11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="T11">
         <v>0.1775</v>
@@ -1715,16 +1871,16 @@
         <v>0.912</v>
       </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD11">
         <v>2.3</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF11">
         <v>0.1765</v>
@@ -1744,7 +1900,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>3.5</v>
@@ -1756,7 +1912,7 @@
         <v>125</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G12">
         <v>823589</v>
@@ -1815,17 +1971,23 @@
       <c r="Y12">
         <v>0.9654</v>
       </c>
+      <c r="Z12">
+        <v>4</v>
+      </c>
       <c r="AA12" t="s">
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>1.15</v>
+      </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD12">
         <v>4.49</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.1917</v>
@@ -1835,6 +1997,18 @@
       </c>
       <c r="AH12">
         <v>0.16</v>
+      </c>
+      <c r="AI12">
+        <v>-0.49</v>
+      </c>
+      <c r="AJ12">
+        <v>0.49</v>
+      </c>
+      <c r="AK12">
+        <v>-0.65</v>
+      </c>
+      <c r="AL12">
+        <v>0.65</v>
       </c>
       <c r="AM12">
         <v>4.65</v>
@@ -1845,7 +2019,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>5.5</v>
@@ -1857,7 +2031,7 @@
         <v>120</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>823589</v>
@@ -1916,17 +2090,23 @@
       <c r="Y13">
         <v>1.0012</v>
       </c>
+      <c r="Z13">
+        <v>3</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB13">
+        <v>-0.17</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD13">
         <v>5.17</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.2812</v>
@@ -1936,6 +2116,18 @@
       </c>
       <c r="AH13">
         <v>0.16</v>
+      </c>
+      <c r="AI13">
+        <v>-2.17</v>
+      </c>
+      <c r="AJ13">
+        <v>2.17</v>
+      </c>
+      <c r="AK13">
+        <v>-2.33</v>
+      </c>
+      <c r="AL13">
+        <v>2.33</v>
       </c>
       <c r="AM13">
         <v>5.33</v>
@@ -1946,7 +2138,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C14">
         <v>3.5</v>
@@ -1958,13 +2150,13 @@
         <v>-139</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G14">
         <v>824077</v>
       </c>
       <c r="H14" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I14">
         <v>4.4</v>
@@ -2017,17 +2209,23 @@
       <c r="Y14">
         <v>0.9548</v>
       </c>
+      <c r="Z14">
+        <v>2</v>
+      </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB14">
+        <v>0.38</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD14">
         <v>3.72</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.2142</v>
@@ -2037,6 +2235,18 @@
       </c>
       <c r="AH14">
         <v>0.16</v>
+      </c>
+      <c r="AI14">
+        <v>-1.72</v>
+      </c>
+      <c r="AJ14">
+        <v>1.72</v>
+      </c>
+      <c r="AK14">
+        <v>-1.88</v>
+      </c>
+      <c r="AL14">
+        <v>1.88</v>
       </c>
       <c r="AM14">
         <v>3.88</v>
@@ -2047,7 +2257,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2059,7 +2269,7 @@
         <v>-125</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G15">
         <v>824077</v>
@@ -2118,17 +2328,23 @@
       <c r="Y15">
         <v>0.9819</v>
       </c>
+      <c r="Z15">
+        <v>3</v>
+      </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB15">
+        <v>-0.55</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD15">
         <v>3.79</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>0.1823</v>
@@ -2138,6 +2354,18 @@
       </c>
       <c r="AH15">
         <v>0.16</v>
+      </c>
+      <c r="AI15">
+        <v>-0.79</v>
+      </c>
+      <c r="AJ15">
+        <v>0.79</v>
+      </c>
+      <c r="AK15">
+        <v>-0.95</v>
+      </c>
+      <c r="AL15">
+        <v>0.95</v>
       </c>
       <c r="AM15">
         <v>3.95</v>
@@ -2148,10 +2376,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G16">
         <v>823668</v>
@@ -2211,16 +2439,16 @@
         <v>0.9396</v>
       </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD16">
         <v>3.37</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.1859</v>
@@ -2240,7 +2468,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>3.5</v>
@@ -2252,7 +2480,7 @@
         <v>-119</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>823668</v>
@@ -2311,17 +2539,23 @@
       <c r="Y17">
         <v>0.9357</v>
       </c>
+      <c r="Z17">
+        <v>4</v>
+      </c>
       <c r="AA17" t="s">
         <v>44</v>
       </c>
+      <c r="AB17">
+        <v>-0.17</v>
+      </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD17">
         <v>3.17</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.1533</v>
@@ -2331,6 +2565,18 @@
       </c>
       <c r="AH17">
         <v>0.16</v>
+      </c>
+      <c r="AI17">
+        <v>0.83</v>
+      </c>
+      <c r="AJ17">
+        <v>0.83</v>
+      </c>
+      <c r="AK17">
+        <v>0.67</v>
+      </c>
+      <c r="AL17">
+        <v>0.67</v>
       </c>
       <c r="AM17">
         <v>3.33</v>
@@ -2341,7 +2587,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2353,7 +2599,7 @@
         <v>100</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G18">
         <v>824641</v>
@@ -2392,7 +2638,7 @@
         <v>0.373</v>
       </c>
       <c r="S18" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="T18">
         <v>0.2302</v>
@@ -2412,17 +2658,23 @@
       <c r="Y18">
         <v>0.9619</v>
       </c>
+      <c r="Z18">
+        <v>1</v>
+      </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AB18">
+        <v>0.32</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD18">
         <v>4.66</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF18">
         <v>0.2061</v>
@@ -2432,6 +2684,18 @@
       </c>
       <c r="AH18">
         <v>0.16</v>
+      </c>
+      <c r="AI18">
+        <v>-3.66</v>
+      </c>
+      <c r="AJ18">
+        <v>3.66</v>
+      </c>
+      <c r="AK18">
+        <v>-3.82</v>
+      </c>
+      <c r="AL18">
+        <v>3.82</v>
       </c>
       <c r="AM18">
         <v>4.82</v>
@@ -2442,7 +2706,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>5.5</v>
@@ -2454,7 +2718,7 @@
         <v>110</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>824641</v>
@@ -2513,17 +2777,23 @@
       <c r="Y19">
         <v>0.9688</v>
       </c>
+      <c r="Z19">
+        <v>10</v>
+      </c>
       <c r="AA19" t="s">
         <v>44</v>
       </c>
+      <c r="AB19">
+        <v>-0.04</v>
+      </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD19">
         <v>5.3</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.2276</v>
@@ -2533,6 +2803,18 @@
       </c>
       <c r="AH19">
         <v>0.16</v>
+      </c>
+      <c r="AI19">
+        <v>4.7</v>
+      </c>
+      <c r="AJ19">
+        <v>4.7</v>
+      </c>
+      <c r="AK19">
+        <v>4.54</v>
+      </c>
+      <c r="AL19">
+        <v>4.54</v>
       </c>
       <c r="AM19">
         <v>5.46</v>
@@ -2543,7 +2825,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C20">
         <v>2.5</v>
@@ -2555,7 +2837,7 @@
         <v>136</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>824320</v>
@@ -2614,17 +2896,23 @@
       <c r="Y20">
         <v>0.9901</v>
       </c>
+      <c r="Z20">
+        <v>3</v>
+      </c>
       <c r="AA20" t="s">
         <v>44</v>
       </c>
+      <c r="AB20">
+        <v>0.61</v>
+      </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AD20">
         <v>2.95</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.1451</v>
@@ -2634,6 +2922,18 @@
       </c>
       <c r="AH20">
         <v>0.16</v>
+      </c>
+      <c r="AI20">
+        <v>0.05</v>
+      </c>
+      <c r="AJ20">
+        <v>0.05</v>
+      </c>
+      <c r="AK20">
+        <v>-0.11</v>
+      </c>
+      <c r="AL20">
+        <v>0.11</v>
       </c>
       <c r="AM20">
         <v>3.11</v>
@@ -2644,7 +2944,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>4.5</v>
@@ -2659,28 +2959,28 @@
         <v>41</v>
       </c>
       <c r="G21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L21">
         <v>6</v>
       </c>
       <c r="S21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE21" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2688,7 +2988,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C22">
         <v>6.5</v>
@@ -2700,31 +3000,31 @@
         <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L22">
         <v>6</v>
       </c>
       <c r="S22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE22" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2732,7 +3032,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C23">
         <v>3.5</v>
@@ -2744,31 +3044,31 @@
         <v>-109</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L23">
         <v>6</v>
       </c>
       <c r="S23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE23" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2776,7 +3076,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <v>6.5</v>
@@ -2788,31 +3088,34 @@
         <v>117</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
       <c r="S24" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="V24" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="Z24">
+        <v>5</v>
       </c>
       <c r="AA24" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AE24" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
